--- a/データまとめ.xlsx
+++ b/データまとめ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/atsu/lab/Bachelor_Report2023/VRPTW_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E59D99-3AD6-174B-8757-2439AB8A103E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E4866A-27AE-A141-94F4-0ED825159D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22900" yWindow="4140" windowWidth="28300" windowHeight="17440" xr2:uid="{9E73BDA8-2747-944E-8D43-49B8F703FC0A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>CVN</t>
     <phoneticPr fontId="1"/>
@@ -46,7 +46,33 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>C102</t>
+    <t>戦略1</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">センリャク1 </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コスト関数1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>steps 115 CVN 14 CRT 2130 n_neg 7.</t>
+  </si>
+  <si>
+    <t>C104</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>steps 115</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>r101</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>steps 179</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -411,26 +437,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AFAAB61-5EC1-D044-AB37-88BCD8A89B6A}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>25</v>
-      </c>
-      <c r="C2">
-        <v>2320</v>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>2130</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>19</v>
+      </c>
+      <c r="C4">
+        <v>2492</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="B9" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/データまとめ.xlsx
+++ b/データまとめ.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/atsu/lab/Bachelor_Report2023/VRPTW_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E4866A-27AE-A141-94F4-0ED825159D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70621A41-3C7D-F342-AC7B-1303F76C4F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22900" yWindow="4140" windowWidth="28300" windowHeight="17440" xr2:uid="{9E73BDA8-2747-944E-8D43-49B8F703FC0A}"/>
+    <workbookView xWindow="660" yWindow="2040" windowWidth="51200" windowHeight="28300" xr2:uid="{9E73BDA8-2747-944E-8D43-49B8F703FC0A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$B$30</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="23">
   <si>
     <t>CVN</t>
     <phoneticPr fontId="1"/>
@@ -46,33 +50,88 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>戦略1</t>
-    <rPh sb="0" eb="2">
-      <t xml:space="preserve">センリャク1 </t>
+    <t>C104</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>steps 115</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>r101</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>steps 179</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>rc208</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>B1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>C1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>車両数「</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">シャリョウスウ </t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>コスト関数1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>steps 115 CVN 14 CRT 2130 n_neg 7.</t>
-  </si>
-  <si>
-    <t>C104</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>steps 115</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>r101</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>steps 179</t>
+    <t>総移動時間</t>
+    <rPh sb="0" eb="5">
+      <t xml:space="preserve">ソウイドウジカｎ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>steps</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Z</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CR</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -105,10 +164,59 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -119,9 +227,30 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -437,62 +566,937 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AFAAB61-5EC1-D044-AB37-88BCD8A89B6A}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A2:T37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="B1" t="s">
+    <row r="2" spans="1:20">
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:20" ht="21" thickBot="1">
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="21" thickTop="1">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C4">
+        <v>14</v>
+      </c>
+      <c r="D4">
+        <v>2130</v>
+      </c>
+      <c r="E4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="B2" t="s">
+      <c r="G4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4">
+        <v>19</v>
+      </c>
+      <c r="J4">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>2492</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <v>22</v>
+      </c>
+      <c r="J5">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>1886</v>
+      </c>
+      <c r="E6">
+        <v>135</v>
+      </c>
+      <c r="G6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6">
+        <v>21</v>
+      </c>
+      <c r="J6">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>13</v>
+      </c>
+      <c r="D7">
+        <v>2031</v>
+      </c>
+      <c r="E7">
+        <v>144</v>
+      </c>
+      <c r="G7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>25</v>
+      </c>
+      <c r="J7">
+        <v>3192</v>
+      </c>
+      <c r="K7">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>2402</v>
+      </c>
+      <c r="E8">
+        <v>200</v>
+      </c>
+      <c r="G8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8">
+        <v>25</v>
+      </c>
+      <c r="J8">
+        <v>2558</v>
+      </c>
+      <c r="K8">
+        <v>81</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="T8" s="7"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>2496</v>
+      </c>
+      <c r="E9">
+        <v>35</v>
+      </c>
+      <c r="G9" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9">
+        <v>23</v>
+      </c>
+      <c r="J9">
+        <v>2623</v>
+      </c>
+      <c r="K9">
+        <v>36</v>
+      </c>
+      <c r="O9" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="P9" s="6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
+      <c r="Q9" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="S9" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="T9" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>12</v>
+      </c>
+      <c r="D10">
+        <v>1766</v>
+      </c>
+      <c r="E10">
+        <v>90</v>
+      </c>
+      <c r="G10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10">
+        <v>24</v>
+      </c>
+      <c r="J10">
+        <v>3038</v>
+      </c>
+      <c r="K10">
+        <v>74</v>
+      </c>
+      <c r="N10" t="s">
+        <v>7</v>
+      </c>
+      <c r="O10">
         <v>14</v>
       </c>
-      <c r="C3">
+      <c r="P10">
         <v>2130</v>
       </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4">
+      <c r="Q10">
         <v>19</v>
       </c>
-      <c r="C4">
+      <c r="R10">
         <v>2492</v>
       </c>
-      <c r="D4" t="s">
+      <c r="S10">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="B9" t="s">
-        <v>4</v>
+      <c r="T10">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>21</v>
+      </c>
+      <c r="D11">
+        <v>2661</v>
+      </c>
+      <c r="E11">
+        <v>59</v>
+      </c>
+      <c r="G11" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11">
+        <v>23</v>
+      </c>
+      <c r="J11">
+        <v>2446</v>
+      </c>
+      <c r="K11">
+        <v>80</v>
+      </c>
+      <c r="N11" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11">
+        <v>15</v>
+      </c>
+      <c r="P11">
+        <v>2183</v>
+      </c>
+      <c r="Q11">
+        <v>18</v>
+      </c>
+      <c r="R11">
+        <v>2442</v>
+      </c>
+      <c r="S11">
+        <v>7</v>
+      </c>
+      <c r="T11">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+      <c r="D12">
+        <v>1666</v>
+      </c>
+      <c r="E12">
+        <v>81</v>
+      </c>
+      <c r="G12" t="s">
+        <v>4</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="2">
+        <v>22</v>
+      </c>
+      <c r="J12" s="2">
+        <v>2565</v>
+      </c>
+      <c r="K12">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>16</v>
+      </c>
+      <c r="D13">
+        <v>2719</v>
+      </c>
+      <c r="E13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14">
+        <v>25</v>
+      </c>
+      <c r="D14">
+        <v>3192</v>
+      </c>
+      <c r="E14">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>7</v>
+      </c>
+      <c r="D15">
+        <v>2181</v>
+      </c>
+      <c r="E15">
+        <v>24</v>
+      </c>
+      <c r="I15" t="s">
+        <v>0</v>
+      </c>
+      <c r="J15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16">
+        <v>15</v>
+      </c>
+      <c r="D16">
+        <v>2206</v>
+      </c>
+      <c r="E16">
+        <v>106</v>
+      </c>
+      <c r="F16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16">
+        <v>8</v>
+      </c>
+      <c r="J16">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17">
+        <v>25</v>
+      </c>
+      <c r="D17">
+        <v>2558</v>
+      </c>
+      <c r="E17">
+        <v>81</v>
+      </c>
+      <c r="F17" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17">
+        <v>8</v>
+      </c>
+      <c r="J17">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>7</v>
+      </c>
+      <c r="D18">
+        <v>2609</v>
+      </c>
+      <c r="E18">
+        <v>27</v>
+      </c>
+      <c r="F18" t="s">
+        <v>6</v>
+      </c>
+      <c r="H18" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18">
+        <v>7</v>
+      </c>
+      <c r="J18">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>15</v>
+      </c>
+      <c r="D19">
+        <v>2206</v>
+      </c>
+      <c r="E19">
+        <v>106</v>
+      </c>
+      <c r="F19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H19" t="s">
+        <v>10</v>
+      </c>
+      <c r="I19">
+        <v>7</v>
+      </c>
+      <c r="J19">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20">
+        <v>23</v>
+      </c>
+      <c r="D20">
+        <v>2623</v>
+      </c>
+      <c r="E20">
+        <v>36</v>
+      </c>
+      <c r="F20" t="s">
+        <v>6</v>
+      </c>
+      <c r="H20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20">
+        <v>7</v>
+      </c>
+      <c r="J20">
+        <v>2609</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21">
+        <v>7</v>
+      </c>
+      <c r="D21">
+        <v>1671</v>
+      </c>
+      <c r="E21">
+        <v>57</v>
+      </c>
+      <c r="F21" t="s">
+        <v>6</v>
+      </c>
+      <c r="H21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I21">
+        <v>7</v>
+      </c>
+      <c r="J21">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>15</v>
+      </c>
+      <c r="D22">
+        <v>2957</v>
+      </c>
+      <c r="E22">
+        <v>113</v>
+      </c>
+      <c r="F22" t="s">
+        <v>6</v>
+      </c>
+      <c r="H22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22">
+        <v>7</v>
+      </c>
+      <c r="J22">
+        <v>2274</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23">
+        <v>24</v>
+      </c>
+      <c r="D23">
+        <v>3038</v>
+      </c>
+      <c r="E23">
+        <v>74</v>
+      </c>
+      <c r="F23" t="s">
+        <v>6</v>
+      </c>
+      <c r="H23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23">
+        <v>7</v>
+      </c>
+      <c r="J23">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24">
+        <v>7</v>
+      </c>
+      <c r="D24">
+        <v>2274</v>
+      </c>
+      <c r="E24">
+        <v>55</v>
+      </c>
+      <c r="F24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H24" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24">
+        <v>7</v>
+      </c>
+      <c r="J24">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>13</v>
+      </c>
+      <c r="D25">
+        <v>2086</v>
+      </c>
+      <c r="E25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26">
+        <v>23</v>
+      </c>
+      <c r="D26">
+        <v>2446</v>
+      </c>
+      <c r="E26">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27">
+        <v>7</v>
+      </c>
+      <c r="D27">
+        <v>2197</v>
+      </c>
+      <c r="E27">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28">
+        <v>13</v>
+      </c>
+      <c r="D28">
+        <v>2304</v>
+      </c>
+      <c r="E28">
+        <v>158</v>
+      </c>
+      <c r="I28" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>22</v>
+      </c>
+      <c r="D29">
+        <v>2565</v>
+      </c>
+      <c r="E29">
+        <v>51</v>
+      </c>
+      <c r="G29" t="s">
+        <v>2</v>
+      </c>
+      <c r="H29" t="s">
+        <v>7</v>
+      </c>
+      <c r="I29">
+        <v>14</v>
+      </c>
+      <c r="J29">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30">
+        <v>7</v>
+      </c>
+      <c r="D30">
+        <v>1612</v>
+      </c>
+      <c r="E30">
+        <v>54</v>
+      </c>
+      <c r="H30" t="s">
+        <v>8</v>
+      </c>
+      <c r="I30">
+        <v>13</v>
+      </c>
+      <c r="J30">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="H31" t="s">
+        <v>9</v>
+      </c>
+      <c r="I31">
+        <v>12</v>
+      </c>
+      <c r="J31">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="H32" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32">
+        <v>16</v>
+      </c>
+      <c r="J32">
+        <v>2719</v>
+      </c>
+    </row>
+    <row r="33" spans="8:10">
+      <c r="H33" t="s">
+        <v>11</v>
+      </c>
+      <c r="I33">
+        <v>15</v>
+      </c>
+      <c r="J33">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="34" spans="8:10">
+      <c r="H34" t="s">
+        <v>12</v>
+      </c>
+      <c r="I34">
+        <v>15</v>
+      </c>
+      <c r="J34">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="35" spans="8:10">
+      <c r="H35" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35">
+        <v>15</v>
+      </c>
+      <c r="J35">
+        <v>2957</v>
+      </c>
+    </row>
+    <row r="36" spans="8:10">
+      <c r="H36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36">
+        <v>13</v>
+      </c>
+      <c r="J36">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="37" spans="8:10">
+      <c r="H37" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37">
+        <v>13</v>
+      </c>
+      <c r="J37">
+        <v>2304</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B2:B30" xr:uid="{4AFAAB61-5EC1-D044-AB37-88BCD8A89B6A}"/>
+  <mergeCells count="3">
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="S8:T8"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71A9FD05-A8D5-9446-8B2F-D8F4A2A0DDC0}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
